--- a/Analysis/RAG_Ablation/rag_ablation_summary.xlsx
+++ b/Analysis/RAG_Ablation/rag_ablation_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P30"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07223333333333334</v>
+        <v>0.08762962962962963</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08371210449023112</v>
+        <v>0.09844588570951782</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4052429548306364</v>
+        <v>0.3462527705722216</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4181135598918732</v>
+        <v>0.3748991618402746</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6571428571428571</v>
+        <v>0.4888888888888889</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8857142857142857</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="K2" t="n">
-        <v>1.162645272981553</v>
+        <v>1.215244541786335</v>
       </c>
       <c r="L2" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="M2" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="N2" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -571,37 +571,37 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0826952380952381</v>
+        <v>0.08843888888888889</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09004010087994641</v>
+        <v>0.0984084807269822</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3481000976877793</v>
+        <v>0.4887449341866359</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3752564170347303</v>
+        <v>0.5186545397510605</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="K3" t="n">
-        <v>0.06747178531118801</v>
+        <v>0.07234651003446843</v>
       </c>
       <c r="L3" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="M3" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="N3" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -627,43 +627,43 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1400761904761905</v>
+        <v>0.131162962962963</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1543019545947781</v>
+        <v>0.1465134002981683</v>
       </c>
       <c r="G4" t="n">
-        <v>0.08085734033250874</v>
+        <v>0.07325185847118741</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1126507946741822</v>
+        <v>0.08409361404149859</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3714285714285714</v>
+        <v>0.4111111111111111</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7714285714285715</v>
+        <v>0.7</v>
       </c>
       <c r="K4" t="n">
-        <v>0.06747178531118801</v>
+        <v>0.07234651003446843</v>
       </c>
       <c r="L4" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="M4" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="N4" t="n">
-        <v>104</v>
+        <v>270</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9904761904761905</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -683,43 +683,43 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07416666666666667</v>
+        <v>0.08745</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08173738288752652</v>
+        <v>0.09654082327114967</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4588035193248305</v>
+        <v>0.3910888208860451</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4989441651511105</v>
+        <v>0.4128423524877523</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.5888888888888889</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8285714285714286</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="K5" t="n">
-        <v>0.06747178531118801</v>
+        <v>0.07234651003446843</v>
       </c>
       <c r="L5" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="M5" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="N5" t="n">
-        <v>105</v>
+        <v>269</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0.9962962962962963</v>
       </c>
     </row>
     <row r="6">
@@ -739,43 +739,43 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1466333333333333</v>
+        <v>0.1267</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1591874348607793</v>
+        <v>0.1431899292189082</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2279161638619205</v>
+        <v>0.06319016102054625</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2302978534977116</v>
+        <v>0.06748659973596938</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5142857142857142</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6571428571428571</v>
+        <v>0.7444444444444445</v>
       </c>
       <c r="K6" t="n">
-        <v>0.436961032521157</v>
+        <v>0.4476506311584402</v>
       </c>
       <c r="L6" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="M6" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="N6" t="n">
-        <v>105</v>
+        <v>269</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0.9962962962962963</v>
       </c>
     </row>
     <row r="7">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08688571428571429</v>
+        <v>0.09810925925925926</v>
       </c>
       <c r="F7" t="n">
-        <v>0.09943707353511295</v>
+        <v>0.1113689331311799</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4614237118360303</v>
+        <v>0.1822297815883974</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4676007258224126</v>
+        <v>0.1781766487206916</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.4777777777777778</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8285714285714286</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="K7" t="n">
-        <v>0.05034897598837103</v>
+        <v>0.05606244345092111</v>
       </c>
       <c r="L7" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="M7" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="N7" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -851,37 +851,37 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="E8" t="n">
-        <v>0.06994285714285713</v>
+        <v>0.08424629629629629</v>
       </c>
       <c r="F8" t="n">
-        <v>0.07670482717305732</v>
+        <v>0.09413330046208618</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5695043711536448</v>
+        <v>0.3421290982335188</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6132600461467931</v>
+        <v>0.3662705192286889</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5222222222222223</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8857142857142857</v>
+        <v>0.8111111111111111</v>
       </c>
       <c r="K8" t="n">
-        <v>0.07879941514560154</v>
+        <v>0.08465588753422101</v>
       </c>
       <c r="L8" t="n">
-        <v>175</v>
+        <v>450</v>
       </c>
       <c r="M8" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="N8" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -893,7 +893,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -907,37 +907,37 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06117619047619048</v>
+        <v>0.1127148148148148</v>
       </c>
       <c r="F9" t="n">
-        <v>0.07155449842428935</v>
+        <v>0.1246704546143062</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4466569474815844</v>
+        <v>0.226842402644133</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4637728802162537</v>
+        <v>0.2425569668769133</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6571428571428571</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="K9" t="n">
-        <v>1.162645272981553</v>
+        <v>1.215244541786335</v>
       </c>
       <c r="L9" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="M9" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="N9" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -963,37 +963,37 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="E10" t="n">
-        <v>0.07107619047619049</v>
+        <v>0.1045222222222222</v>
       </c>
       <c r="F10" t="n">
-        <v>0.08256779540103024</v>
+        <v>0.1209496976535898</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3418950427196796</v>
+        <v>0.187224112063766</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3494871659305394</v>
+        <v>0.168155273291284</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7714285714285715</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="K10" t="n">
-        <v>0.06747178531118801</v>
+        <v>0.07234651003446843</v>
       </c>
       <c r="L10" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="M10" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="N10" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1005,7 +1005,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1019,49 +1019,49 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1427023809523809</v>
+        <v>0.157687037037037</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1625661014366155</v>
+        <v>0.1770408262143761</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1047619047619048</v>
+        <v>0.06092403608438213</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1</v>
+        <v>0.06517806004204932</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="K11" t="n">
-        <v>0.06747178531118801</v>
+        <v>0.07234651003446843</v>
       </c>
       <c r="L11" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="M11" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="N11" t="n">
-        <v>104</v>
+        <v>270</v>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9904761904761905</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1075,37 +1075,37 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="E12" t="n">
-        <v>0.07246190476190476</v>
+        <v>0.1058314814814815</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0840112362067819</v>
+        <v>0.1212250654862602</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3090427594550779</v>
+        <v>0.175364700845739</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3104578686795554</v>
+        <v>0.1844230690150369</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="K12" t="n">
-        <v>0.06747178531118801</v>
+        <v>0.07234651003446843</v>
       </c>
       <c r="L12" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="M12" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="N12" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1117,7 +1117,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1131,37 +1131,37 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1511857142857143</v>
+        <v>0.1634185185185185</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1687703437290628</v>
+        <v>0.1840832746767171</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.02332847374079218</v>
+        <v>0.02222222222222222</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.03902929725098397</v>
+        <v>0.02222222222222222</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3142857142857143</v>
+        <v>0.3444444444444444</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.6888888888888889</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4267642604453223</v>
+        <v>0.4469366408056682</v>
       </c>
       <c r="L13" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="M13" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="N13" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1187,49 +1187,49 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="E14" t="n">
-        <v>0.08313809523809522</v>
+        <v>0.1182425925925926</v>
       </c>
       <c r="F14" t="n">
-        <v>0.09618846002439888</v>
+        <v>0.1377323535264282</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.2366628869835791</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3382352941176471</v>
+        <v>0.2303561200840986</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5142857142857142</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="K14" t="n">
-        <v>0.05034897598837103</v>
+        <v>0.05606244345092111</v>
       </c>
       <c r="L14" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="M14" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="N14" t="n">
-        <v>101</v>
+        <v>270</v>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9619047619047619</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1243,37 +1243,37 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="E15" t="n">
-        <v>0.06045714285714286</v>
+        <v>0.1016333333333333</v>
       </c>
       <c r="F15" t="n">
-        <v>0.06867990815697501</v>
+        <v>0.1162007893965204</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4804713308836492</v>
+        <v>0.1123595505617977</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5247435829652698</v>
+        <v>0.1179775280898876</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6857142857142857</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8857142857142857</v>
+        <v>0.7</v>
       </c>
       <c r="K15" t="n">
-        <v>0.07879941514560154</v>
+        <v>0.08465588753422101</v>
       </c>
       <c r="L15" t="n">
-        <v>175</v>
+        <v>450</v>
       </c>
       <c r="M15" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="N15" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -1285,107 +1285,105 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>offline</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>alternate_embedding_k3</t>
+          <t>nearest_neighbor_k3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Alternate embedding k=3 (sentence-transformers/paraphrase-MiniLM-L3-v2)</t>
+          <t>Nearest-neighbor prediction k=3</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0933095238095238</v>
+        <v>0.1009487654320988</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1085050456266304</v>
+        <v>0.1159090834373691</v>
       </c>
       <c r="G16" t="n">
-        <v>0.219047619047619</v>
+        <v>0.001122450160373804</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2142857142857143</v>
+        <v>0.01726497308103742</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4857142857142857</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="K16" t="n">
-        <v>1.162645272981553</v>
+        <v>0.07234651003446843</v>
       </c>
       <c r="L16" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="M16" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="P16" t="n">
-        <v>1</v>
-      </c>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>control_k3</t>
+          <t>alternate_embedding_k3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Control k=3 standard</t>
+          <t>Alternate embedding k=3 (sentence-transformers/paraphrase-MiniLM-L3-v2)</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="E17" t="n">
-        <v>0.08698095238095239</v>
+        <v>0.1039240740740741</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1003733706698447</v>
+        <v>0.1163438491525867</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2</v>
+        <v>0.1651380096338454</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2428571428571429</v>
+        <v>0.1639994160049554</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4857142857142857</v>
+        <v>0.4777777777777778</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="K17" t="n">
-        <v>0.06747178531118801</v>
+        <v>1.215244541786335</v>
       </c>
       <c r="L17" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="M17" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="N17" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -1397,51 +1395,51 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>descriptions_no_scores_ranks</t>
+          <t>control_k3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Descriptions without scores or ranks</t>
+          <t>Control k=3 standard</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="E18" t="n">
-        <v>0.143047619047619</v>
+        <v>0.1019388888888889</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1638109194398649</v>
+        <v>0.1199781682358509</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.06514636103821395</v>
+        <v>0.1535166286769747</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.08684925466013452</v>
+        <v>0.1540669489309382</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3142857142857143</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.7444444444444445</v>
       </c>
       <c r="K18" t="n">
-        <v>0.06747178531118801</v>
+        <v>0.07234651003446843</v>
       </c>
       <c r="L18" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="M18" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="N18" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -1453,51 +1451,51 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>exemplars_no_hidden_params</t>
+          <t>descriptions_no_scores_ranks</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Exemplars without hidden parameters</t>
+          <t>Descriptions without scores or ranks</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="E19" t="n">
-        <v>0.09344285714285711</v>
+        <v>0.1510611111111111</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1080892889444873</v>
+        <v>0.1683096172315921</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2</v>
+        <v>0.07107475194335945</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2285714285714286</v>
+        <v>0.0762525815656961</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4571428571428571</v>
+        <v>0.4222222222222222</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="K19" t="n">
-        <v>0.06747178531118801</v>
+        <v>0.07234651003446843</v>
       </c>
       <c r="L19" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="M19" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="N19" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -1509,51 +1507,51 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>random_exemplars_k3</t>
+          <t>exemplars_no_hidden_params</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Random exemplars k=3</t>
+          <t>Exemplars without hidden parameters</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1731571428571428</v>
+        <v>0.09876851851851852</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1931280170343895</v>
+        <v>0.1135721691612731</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.03381438340206498</v>
+        <v>0.2730298857137317</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.04668498846330175</v>
+        <v>0.2778882113209986</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.7444444444444445</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4337207845279149</v>
+        <v>0.07234651003446843</v>
       </c>
       <c r="L20" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="M20" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="N20" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -1565,51 +1563,51 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>retrieval_k1</t>
+          <t>random_exemplars_k3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Retrieval k=1</t>
+          <t>Random exemplars k=3</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0986952380952381</v>
+        <v>0.1407148148148148</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1120815657192272</v>
+        <v>0.1568488307766427</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2676287668041299</v>
+        <v>0.2756401421058631</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2933699769266035</v>
+        <v>0.2969461037109608</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5777777777777777</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7714285714285715</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="K21" t="n">
-        <v>0.05034897598837103</v>
+        <v>0.4557924783340206</v>
       </c>
       <c r="L21" t="n">
-        <v>35</v>
+        <v>270</v>
       </c>
       <c r="M21" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="N21" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -1621,51 +1619,51 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>retrieval_k5</t>
+          <t>retrieval_k1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Retrieval k=5</t>
+          <t>Retrieval k=1</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0922904761904762</v>
+        <v>0.09683148148148146</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1050175147143705</v>
+        <v>0.1127899191896223</v>
       </c>
       <c r="G22" t="n">
-        <v>0.328090378502697</v>
+        <v>0.3056026889223424</v>
       </c>
       <c r="H22" t="n">
-        <v>0.339029297250984</v>
+        <v>0.2969461037109608</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5142857142857142</v>
+        <v>0.5222222222222223</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8285714285714286</v>
+        <v>0.8222222222222222</v>
       </c>
       <c r="K22" t="n">
-        <v>0.07879941514560154</v>
+        <v>0.05606244345092111</v>
       </c>
       <c r="L22" t="n">
-        <v>175</v>
+        <v>90</v>
       </c>
       <c r="M22" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="N22" t="n">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -1677,446 +1675,56 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>offline</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nearest_neighbor_k3</t>
+          <t>retrieval_k5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nearest-neighbor prediction k=3</t>
+          <t>Retrieval k=5</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="E23" t="n">
-        <v>0.09595132275132275</v>
+        <v>0.08795370370370369</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1073600431534542</v>
+        <v>0.1001909253429351</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.03888078956798696</v>
+        <v>0.2342775026800086</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.04123930494211613</v>
+        <v>0.2708296301895526</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4571428571428571</v>
+        <v>0.4888888888888889</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6857142857142857</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="K23" t="n">
-        <v>0.06747178531118801</v>
+        <v>0.08465588753422101</v>
       </c>
       <c r="L23" t="n">
-        <v>105</v>
+        <v>450</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="P23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>qwen</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>alternate_embedding_k3</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Alternate embedding k=3 (sentence-transformers/paraphrase-MiniLM-L3-v2)</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>35</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.09594761904761905</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.1111740852087775</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.2289065610622504</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.2675904768045093</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.4571428571428571</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.6857142857142857</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1.162645272981553</v>
-      </c>
-      <c r="L24" t="n">
-        <v>105</v>
-      </c>
-      <c r="M24" t="n">
-        <v>105</v>
-      </c>
-      <c r="N24" t="n">
-        <v>105</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>qwen</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>control_k3</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Control k=3 standard</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>35</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.1029428571428571</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.1195368390626066</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.3772572649328235</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.3817598851925247</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.7714285714285715</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.06747178531118801</v>
-      </c>
-      <c r="L25" t="n">
-        <v>105</v>
-      </c>
-      <c r="M25" t="n">
-        <v>105</v>
-      </c>
-      <c r="N25" t="n">
-        <v>105</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>qwen</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>descriptions_no_scores_ranks</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Descriptions without scores or ranks</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>35</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.1413952380952381</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.1566989002260409</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.3156307950900595</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.3281856672400665</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.8285714285714286</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0.06747178531118801</v>
-      </c>
-      <c r="L26" t="n">
-        <v>105</v>
-      </c>
-      <c r="M26" t="n">
-        <v>105</v>
-      </c>
-      <c r="N26" t="n">
-        <v>105</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>qwen</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>exemplars_no_hidden_params</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Exemplars without hidden parameters</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>35</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.1014333333333333</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.1211903349485712</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.2323232323232323</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.2272727272727273</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.4571428571428571</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.8285714285714286</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0.06747178531118801</v>
-      </c>
-      <c r="L27" t="n">
-        <v>105</v>
-      </c>
-      <c r="M27" t="n">
-        <v>105</v>
-      </c>
-      <c r="N27" t="n">
-        <v>105</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>qwen</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>random_exemplars_k3</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Random exemplars k=3</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>35</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.1362857142857143</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.1528303975016928</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.08182849004478429</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.09902876340700373</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.5142857142857142</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.6571428571428571</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0.436440634727478</v>
-      </c>
-      <c r="L28" t="n">
-        <v>105</v>
-      </c>
-      <c r="M28" t="n">
-        <v>105</v>
-      </c>
-      <c r="N28" t="n">
-        <v>105</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>qwen</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>retrieval_k1</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Retrieval k=1</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>35</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.1022761904761905</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.1168140111505223</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.3725490196078431</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.4264705882352941</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.6285714285714286</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0.05034897598837103</v>
-      </c>
-      <c r="L29" t="n">
-        <v>35</v>
-      </c>
-      <c r="M29" t="n">
-        <v>105</v>
-      </c>
-      <c r="N29" t="n">
-        <v>105</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>qwen</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>retrieval_k5</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Retrieval k=5</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>35</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.09163809523809523</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.106920177701447</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.1617647058823529</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.4285714285714285</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.6857142857142857</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0.07879941514560154</v>
-      </c>
-      <c r="L30" t="n">
-        <v>175</v>
-      </c>
-      <c r="M30" t="n">
-        <v>105</v>
-      </c>
-      <c r="N30" t="n">
-        <v>105</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
+      <c r="P23" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Analysis/RAG_Ablation/rag_ablation_summary.xlsx
+++ b/Analysis/RAG_Ablation/rag_ablation_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -592,7 +592,7 @@
         <v>0.8888888888888888</v>
       </c>
       <c r="K3" t="n">
-        <v>0.07234651003446843</v>
+        <v>0.07234651003446844</v>
       </c>
       <c r="L3" t="n">
         <v>270</v>
@@ -636,7 +636,7 @@
         <v>0.1465134002981683</v>
       </c>
       <c r="G4" t="n">
-        <v>0.07325185847118741</v>
+        <v>0.07325185847118743</v>
       </c>
       <c r="H4" t="n">
         <v>0.08409361404149859</v>
@@ -648,7 +648,7 @@
         <v>0.7</v>
       </c>
       <c r="K4" t="n">
-        <v>0.07234651003446843</v>
+        <v>0.07234651003446844</v>
       </c>
       <c r="L4" t="n">
         <v>270</v>
@@ -686,7 +686,7 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08745</v>
+        <v>0.08744999999999997</v>
       </c>
       <c r="F5" t="n">
         <v>0.09654082327114967</v>
@@ -704,7 +704,7 @@
         <v>0.8444444444444444</v>
       </c>
       <c r="K5" t="n">
-        <v>0.07234651003446843</v>
+        <v>0.07234651003446844</v>
       </c>
       <c r="L5" t="n">
         <v>270</v>
@@ -893,7 +893,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -910,22 +910,22 @@
         <v>90</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1127148148148148</v>
+        <v>0.07113148148148148</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1246704546143062</v>
+        <v>0.07950886807601082</v>
       </c>
       <c r="G9" t="n">
-        <v>0.226842402644133</v>
+        <v>0.5173960683581447</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2425569668769133</v>
+        <v>0.5577350269189626</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="K9" t="n">
         <v>1.215244541786335</v>
@@ -949,7 +949,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -966,25 +966,25 @@
         <v>90</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1045222222222222</v>
+        <v>0.07047777777777779</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1209496976535898</v>
+        <v>0.08011953885543749</v>
       </c>
       <c r="G10" t="n">
-        <v>0.187224112063766</v>
+        <v>0.3868499620103081</v>
       </c>
       <c r="H10" t="n">
-        <v>0.168155273291284</v>
+        <v>0.4040669489309383</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8111111111111111</v>
       </c>
       <c r="K10" t="n">
-        <v>0.07234651003446843</v>
+        <v>0.07234651003446844</v>
       </c>
       <c r="L10" t="n">
         <v>270</v>
@@ -1005,7 +1005,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1022,25 +1022,25 @@
         <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>0.157687037037037</v>
+        <v>0.1426777777777778</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1770408262143761</v>
+        <v>0.1618571696309349</v>
       </c>
       <c r="G11" t="n">
-        <v>0.06092403608438213</v>
+        <v>0.2037037037037037</v>
       </c>
       <c r="H11" t="n">
-        <v>0.06517806004204932</v>
+        <v>0.2166666666666667</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7111111111111111</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="K11" t="n">
-        <v>0.07234651003446843</v>
+        <v>0.07234651003446844</v>
       </c>
       <c r="L11" t="n">
         <v>270</v>
@@ -1061,7 +1061,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1078,25 +1078,25 @@
         <v>90</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1058314814814815</v>
+        <v>0.0779425925925926</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1212250654862602</v>
+        <v>0.08919822331935418</v>
       </c>
       <c r="G12" t="n">
-        <v>0.175364700845739</v>
+        <v>0.4366628869835791</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1844230690150369</v>
+        <v>0.4470227867507653</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7111111111111111</v>
+        <v>0.8</v>
       </c>
       <c r="K12" t="n">
-        <v>0.07234651003446843</v>
+        <v>0.07234651003446844</v>
       </c>
       <c r="L12" t="n">
         <v>270</v>
@@ -1117,7 +1117,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1134,25 +1134,25 @@
         <v>90</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1634185185185185</v>
+        <v>0.1391074074074074</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1840832746767171</v>
+        <v>0.1565049139254751</v>
       </c>
       <c r="G13" t="n">
-        <v>0.02222222222222222</v>
+        <v>0.1774036277243198</v>
       </c>
       <c r="H13" t="n">
-        <v>0.02222222222222222</v>
+        <v>0.1803561200840987</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3444444444444444</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6888888888888889</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4469366408056682</v>
+        <v>0.4469366408056683</v>
       </c>
       <c r="L13" t="n">
         <v>270</v>
@@ -1173,7 +1173,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1190,22 +1190,22 @@
         <v>90</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1182425925925926</v>
+        <v>0.09680925925925926</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1377323535264282</v>
+        <v>0.1087835686834211</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2366628869835791</v>
+        <v>0.3774036277243198</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2303561200840986</v>
+        <v>0.3748005645285432</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.5777777777777777</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="K14" t="n">
         <v>0.05606244345092111</v>
@@ -1229,7 +1229,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1246,22 +1246,22 @@
         <v>90</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1016333333333333</v>
+        <v>0.06913888888888887</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1162007893965204</v>
+        <v>0.07775558831547687</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1123595505617977</v>
+        <v>0.4312944064547524</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1179775280898876</v>
+        <v>0.4429558378198271</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.6444444444444445</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7</v>
+        <v>0.8222222222222222</v>
       </c>
       <c r="K15" t="n">
         <v>0.08465588753422101</v>
@@ -1285,96 +1285,98 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>offline</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nearest_neighbor_k3</t>
+          <t>alternate_embedding_k3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nearest-neighbor prediction k=3</t>
+          <t>Alternate embedding k=3 (sentence-transformers/paraphrase-MiniLM-L3-v2)</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>90</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1009487654320988</v>
+        <v>0.1127148148148148</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1159090834373691</v>
+        <v>0.1246704546143062</v>
       </c>
       <c r="G16" t="n">
-        <v>0.001122450160373804</v>
+        <v>0.226842402644133</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01726497308103742</v>
+        <v>0.2425569668769133</v>
       </c>
       <c r="I16" t="n">
         <v>0.4444444444444444</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="K16" t="n">
-        <v>0.07234651003446843</v>
+        <v>1.215244541786335</v>
       </c>
       <c r="L16" t="n">
         <v>270</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="P16" t="inlineStr"/>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>alternate_embedding_k3</t>
+          <t>control_k3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Alternate embedding k=3 (sentence-transformers/paraphrase-MiniLM-L3-v2)</t>
+          <t>Control k=3 standard</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>90</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1039240740740741</v>
+        <v>0.1045222222222222</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1163438491525867</v>
+        <v>0.1209496976535897</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1651380096338454</v>
+        <v>0.187224112063766</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1639994160049554</v>
+        <v>0.168155273291284</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4777777777777778</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="K17" t="n">
-        <v>1.215244541786335</v>
+        <v>0.07234651003446844</v>
       </c>
       <c r="L17" t="n">
         <v>270</v>
@@ -1395,42 +1397,42 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>control_k3</t>
+          <t>descriptions_no_scores_ranks</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Control k=3 standard</t>
+          <t>Descriptions without scores or ranks</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>90</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1019388888888889</v>
+        <v>0.157687037037037</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1199781682358509</v>
+        <v>0.1770408262143761</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1535166286769747</v>
+        <v>0.06092403608438215</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1540669489309382</v>
+        <v>0.06517806004204932</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7444444444444445</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="K18" t="n">
-        <v>0.07234651003446843</v>
+        <v>0.07234651003446844</v>
       </c>
       <c r="L18" t="n">
         <v>270</v>
@@ -1451,42 +1453,42 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>descriptions_no_scores_ranks</t>
+          <t>exemplars_no_hidden_params</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Descriptions without scores or ranks</t>
+          <t>Exemplars without hidden parameters</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>90</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1510611111111111</v>
+        <v>0.1058314814814815</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1683096172315921</v>
+        <v>0.1212250654862602</v>
       </c>
       <c r="G19" t="n">
-        <v>0.07107475194335945</v>
+        <v>0.175364700845739</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0762525815656961</v>
+        <v>0.1844230690150369</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4222222222222222</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="K19" t="n">
-        <v>0.07234651003446843</v>
+        <v>0.07234651003446844</v>
       </c>
       <c r="L19" t="n">
         <v>270</v>
@@ -1507,42 +1509,42 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exemplars_no_hidden_params</t>
+          <t>random_exemplars_k3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Exemplars without hidden parameters</t>
+          <t>Random exemplars k=3</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>90</v>
       </c>
       <c r="E20" t="n">
-        <v>0.09876851851851852</v>
+        <v>0.1634185185185185</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1135721691612731</v>
+        <v>0.1840832746767171</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2730298857137317</v>
+        <v>0.02222222222222222</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2778882113209986</v>
+        <v>0.02222222222222222</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.3444444444444444</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7444444444444445</v>
+        <v>0.6888888888888889</v>
       </c>
       <c r="K20" t="n">
-        <v>0.07234651003446843</v>
+        <v>0.4469366408056683</v>
       </c>
       <c r="L20" t="n">
         <v>270</v>
@@ -1563,45 +1565,45 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>random_exemplars_k3</t>
+          <t>retrieval_k1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Random exemplars k=3</t>
+          <t>Retrieval k=1</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>90</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1407148148148148</v>
+        <v>0.1182425925925926</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1568488307766427</v>
+        <v>0.1377323535264282</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2756401421058631</v>
+        <v>0.2366628869835791</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2969461037109608</v>
+        <v>0.2303561200840986</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5777777777777777</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8444444444444444</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4557924783340206</v>
+        <v>0.05606244345092111</v>
       </c>
       <c r="L21" t="n">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="M21" t="n">
         <v>270</v>
@@ -1619,45 +1621,45 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>retrieval_k1</t>
+          <t>retrieval_k5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Retrieval k=1</t>
+          <t>Retrieval k=5</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>90</v>
       </c>
       <c r="E22" t="n">
-        <v>0.09683148148148146</v>
+        <v>0.1016333333333333</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1127899191896223</v>
+        <v>0.1162007893965204</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3056026889223424</v>
+        <v>0.1123595505617977</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2969461037109608</v>
+        <v>0.1179775280898876</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5222222222222223</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8222222222222222</v>
+        <v>0.7</v>
       </c>
       <c r="K22" t="n">
-        <v>0.05606244345092111</v>
+        <v>0.08465588753422101</v>
       </c>
       <c r="L22" t="n">
-        <v>90</v>
+        <v>450</v>
       </c>
       <c r="M22" t="n">
         <v>270</v>
@@ -1675,56 +1677,446 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>nearest_neighbor_k3</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Nearest-neighbor prediction k=3</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>90</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.1009487654320988</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.1159090834373691</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.001122450160373804</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.01726497308103742</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.07234651003446844</v>
+      </c>
+      <c r="L23" t="n">
+        <v>270</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>qwen</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>alternate_embedding_k3</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Alternate embedding k=3 (sentence-transformers/paraphrase-MiniLM-L3-v2)</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>90</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.1039240740740741</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.1163438491525867</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.1651380096338454</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1639994160049554</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.4777777777777778</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.215244541786335</v>
+      </c>
+      <c r="L24" t="n">
+        <v>270</v>
+      </c>
+      <c r="M24" t="n">
+        <v>270</v>
+      </c>
+      <c r="N24" t="n">
+        <v>270</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>control_k3</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Control k=3 standard</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>90</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.1019388888888889</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.1199781682358509</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.1535166286769747</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.1540669489309382</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.4333333333333333</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.7444444444444445</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.07234651003446844</v>
+      </c>
+      <c r="L25" t="n">
+        <v>270</v>
+      </c>
+      <c r="M25" t="n">
+        <v>270</v>
+      </c>
+      <c r="N25" t="n">
+        <v>270</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>descriptions_no_scores_ranks</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Descriptions without scores or ranks</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>90</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.1510611111111111</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.1683096172315921</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.07107475194335945</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.0762525815656961</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.4222222222222222</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.7555555555555555</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.07234651003446844</v>
+      </c>
+      <c r="L26" t="n">
+        <v>270</v>
+      </c>
+      <c r="M26" t="n">
+        <v>270</v>
+      </c>
+      <c r="N26" t="n">
+        <v>270</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>exemplars_no_hidden_params</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Exemplars without hidden parameters</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>90</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.09876851851851849</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.1135721691612731</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.2730298857137317</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.2778882113209986</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.7444444444444445</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.07234651003446844</v>
+      </c>
+      <c r="L27" t="n">
+        <v>270</v>
+      </c>
+      <c r="M27" t="n">
+        <v>270</v>
+      </c>
+      <c r="N27" t="n">
+        <v>270</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>random_exemplars_k3</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Random exemplars k=3</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>90</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.1407148148148148</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.1568488307766427</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.275640142105863</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.2969461037109608</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.5777777777777777</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.8444444444444444</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.4557924783340208</v>
+      </c>
+      <c r="L28" t="n">
+        <v>270</v>
+      </c>
+      <c r="M28" t="n">
+        <v>270</v>
+      </c>
+      <c r="N28" t="n">
+        <v>270</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>retrieval_k1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Retrieval k=1</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>90</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.09683148148148148</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.1127899191896223</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.3056026889223424</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.2969461037109608</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.5222222222222223</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.8222222222222222</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.05606244345092111</v>
+      </c>
+      <c r="L29" t="n">
+        <v>90</v>
+      </c>
+      <c r="M29" t="n">
+        <v>270</v>
+      </c>
+      <c r="N29" t="n">
+        <v>270</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
         <is>
           <t>retrieval_k5</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Retrieval k=5</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>90</v>
-      </c>
-      <c r="E23" t="n">
+      <c r="D30" t="n">
+        <v>90</v>
+      </c>
+      <c r="E30" t="n">
         <v>0.08795370370370369</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F30" t="n">
         <v>0.1001909253429351</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G30" t="n">
         <v>0.2342775026800086</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H30" t="n">
         <v>0.2708296301895526</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I30" t="n">
         <v>0.4888888888888889</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J30" t="n">
         <v>0.7666666666666667</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K30" t="n">
         <v>0.08465588753422101</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L30" t="n">
         <v>450</v>
       </c>
-      <c r="M23" t="n">
-        <v>270</v>
-      </c>
-      <c r="N23" t="n">
-        <v>270</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="M30" t="n">
+        <v>270</v>
+      </c>
+      <c r="N30" t="n">
+        <v>270</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
         <v>1</v>
       </c>
     </row>
